--- a/main/ig/StructureDefinition-ror-practitioner.xlsx
+++ b/main/ig/StructureDefinition-ror-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-21T15:54:27+00:00</t>
+    <t>2026-01-30T10:12:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-ror-practitioner.xlsx
+++ b/main/ig/StructureDefinition-ror-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-30T10:12:59+00:00</t>
+    <t>2026-03-09T13:22:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-ror-practitioner.xlsx
+++ b/main/ig/StructureDefinition-ror-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-09T13:22:43+00:00</t>
+    <t>2026-03-17T11:12:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-ror-practitioner.xlsx
+++ b/main/ig/StructureDefinition-ror-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-17T11:12:47+00:00</t>
+    <t>2026-03-23T15:20:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-ror-practitioner.xlsx
+++ b/main/ig/StructureDefinition-ror-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-23T15:20:38+00:00</t>
+    <t>2026-03-24T09:51:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-ror-practitioner.xlsx
+++ b/main/ig/StructureDefinition-ror-practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0-snapshot-1</t>
+    <t>0.7.0-snapshot-2</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-24T09:51:35+00:00</t>
+    <t>2026-03-24T10:30:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-ror-practitioner.xlsx
+++ b/main/ig/StructureDefinition-ror-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T08:33:49+00:00</t>
+    <t>2026-04-29T13:16:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-ror-practitioner.xlsx
+++ b/main/ig/StructureDefinition-ror-practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0-snapshot-2</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T13:16:27+00:00</t>
+    <t>2026-04-29T15:21:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-ror-practitioner.xlsx
+++ b/main/ig/StructureDefinition-ror-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T15:21:13+00:00</t>
+    <t>2026-04-29T15:21:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-ror-practitioner.xlsx
+++ b/main/ig/StructureDefinition-ror-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T15:21:33+00:00</t>
+    <t>2026-07-23T07:54:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -458,7 +458,7 @@
     <t>Practitioner.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -496,7 +496,7 @@
     <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -526,7 +526,7 @@
     <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
+    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
   </si>
   <si>
     <t>Slicing pour gérer le code région définissant la région source des données</t>
@@ -587,7 +587,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -772,7 +772,7 @@
     <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -877,7 +877,7 @@
     <t>Practitioner.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -1951,17 +1951,17 @@
   <dimension ref="A1:AO64"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="63.25390625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="40.70703125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="34.48828125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="54.23046875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="34.8984375" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="29.5703125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="138.9140625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="119.09375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1970,27 +1970,27 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="38.2265625" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="98.61328125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="81.53515625" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="69.203125" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="34.859375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="32.7734375" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="84.54296875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="69.90234375" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="59.33203125" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="29.88671875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="54.96875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="62.87890625" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="102.6171875" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="52.3828125" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="47.125" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="53.91015625" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="87.9765625" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="44.90625" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="31.65234375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2814,7 +2814,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="8" hidden="true">
+    <row r="8">
       <c r="A8" t="s" s="2">
         <v>128</v>
       </c>
@@ -3399,7 +3399,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="13" hidden="true">
+    <row r="13">
       <c r="A13" t="s" s="2">
         <v>167</v>
       </c>
@@ -4099,7 +4099,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
         <v>205</v>
       </c>
@@ -4335,7 +4335,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="21" hidden="true">
+    <row r="21">
       <c r="A21" t="s" s="2">
         <v>215</v>
       </c>
@@ -6336,7 +6336,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
         <v>343</v>
       </c>
@@ -6687,7 +6687,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="41" hidden="true">
+    <row r="41">
       <c r="A41" t="s" s="2">
         <v>366</v>
       </c>
@@ -7036,7 +7036,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="44" hidden="true">
+    <row r="44">
       <c r="A44" t="s" s="2">
         <v>380</v>
       </c>
@@ -7153,7 +7153,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="45" hidden="true">
+    <row r="45">
       <c r="A45" t="s" s="2">
         <v>385</v>
       </c>
@@ -7270,7 +7270,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="46" hidden="true">
+    <row r="46">
       <c r="A46" t="s" s="2">
         <v>390</v>
       </c>
@@ -7504,7 +7504,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="48" hidden="true">
+    <row r="48">
       <c r="A48" t="s" s="2">
         <v>405</v>
       </c>
@@ -9507,12 +9507,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AO64">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>

--- a/main/ig/StructureDefinition-ror-practitioner.xlsx
+++ b/main/ig/StructureDefinition-ror-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T07:54:45+00:00</t>
+    <t>2026-07-23T08:00:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-ror-practitioner.xlsx
+++ b/main/ig/StructureDefinition-ror-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T08:00:07+00:00</t>
+    <t>2026-07-23T08:13:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
